--- a/data/history/long/history_long.xlsx
+++ b/data/history/long/history_long.xlsx
@@ -6027,9 +6027,6 @@
       <c r="A66" t="s">
         <v>65</v>
       </c>
-      <c r="G66">
-        <v>-100</v>
-      </c>
       <c r="H66">
         <v>20.96666666666667</v>
       </c>
@@ -7287,12 +7284,6 @@
       <c r="A93" t="s">
         <v>92</v>
       </c>
-      <c r="J93">
-        <v>-100</v>
-      </c>
-      <c r="K93">
-        <v>-100</v>
-      </c>
       <c r="L93">
         <v>-27.40833333333333</v>
       </c>
@@ -7331,12 +7322,6 @@
       <c r="A94" t="s">
         <v>93</v>
       </c>
-      <c r="J94">
-        <v>-100</v>
-      </c>
-      <c r="K94">
-        <v>-100</v>
-      </c>
       <c r="L94">
         <v>-3.066666666666666</v>
       </c>
@@ -7374,12 +7359,6 @@
     <row r="95" spans="1:22">
       <c r="A95" t="s">
         <v>94</v>
-      </c>
-      <c r="J95">
-        <v>-100</v>
-      </c>
-      <c r="K95">
-        <v>-100</v>
       </c>
       <c r="L95">
         <v>-6.683333333333334</v>
@@ -13218,13 +13197,13 @@
         <v>450</v>
       </c>
       <c r="F65">
-        <v>2010</v>
+        <v>2011</v>
       </c>
       <c r="G65">
         <v>2025</v>
       </c>
       <c r="H65">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="66" spans="1:8">
@@ -13920,13 +13899,13 @@
         <v>469</v>
       </c>
       <c r="F92">
-        <v>2013</v>
+        <v>2015</v>
       </c>
       <c r="G92">
         <v>2025</v>
       </c>
       <c r="H92">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="93" spans="1:8">
@@ -13946,13 +13925,13 @@
         <v>470</v>
       </c>
       <c r="F93">
-        <v>2013</v>
+        <v>2015</v>
       </c>
       <c r="G93">
         <v>2025</v>
       </c>
       <c r="H93">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="94" spans="1:8">
@@ -13972,13 +13951,13 @@
         <v>471</v>
       </c>
       <c r="F94">
-        <v>2013</v>
+        <v>2015</v>
       </c>
       <c r="G94">
         <v>2025</v>
       </c>
       <c r="H94">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="95" spans="1:8">
@@ -29354,18 +29333,6 @@
       <c r="A37" t="s">
         <v>65</v>
       </c>
-      <c r="V37">
-        <v>-100</v>
-      </c>
-      <c r="W37">
-        <v>-100</v>
-      </c>
-      <c r="X37">
-        <v>-100</v>
-      </c>
-      <c r="Y37">
-        <v>-100</v>
-      </c>
       <c r="Z37">
         <v>18.53333333333333</v>
       </c>
@@ -34181,30 +34148,6 @@
       <c r="A64" t="s">
         <v>92</v>
       </c>
-      <c r="AH64">
-        <v>-100</v>
-      </c>
-      <c r="AI64">
-        <v>-100</v>
-      </c>
-      <c r="AJ64">
-        <v>-100</v>
-      </c>
-      <c r="AK64">
-        <v>-100</v>
-      </c>
-      <c r="AL64">
-        <v>-100</v>
-      </c>
-      <c r="AM64">
-        <v>-100</v>
-      </c>
-      <c r="AN64">
-        <v>-100</v>
-      </c>
-      <c r="AO64">
-        <v>-100</v>
-      </c>
       <c r="AP64">
         <v>-55.7</v>
       </c>
@@ -34348,30 +34291,6 @@
       <c r="A65" t="s">
         <v>93</v>
       </c>
-      <c r="AH65">
-        <v>-100</v>
-      </c>
-      <c r="AI65">
-        <v>-100</v>
-      </c>
-      <c r="AJ65">
-        <v>-100</v>
-      </c>
-      <c r="AK65">
-        <v>-100</v>
-      </c>
-      <c r="AL65">
-        <v>-100</v>
-      </c>
-      <c r="AM65">
-        <v>-100</v>
-      </c>
-      <c r="AN65">
-        <v>-100</v>
-      </c>
-      <c r="AO65">
-        <v>-100</v>
-      </c>
       <c r="AP65">
         <v>-2.800000000000002</v>
       </c>
@@ -34514,30 +34433,6 @@
     <row r="66" spans="1:88">
       <c r="A66" t="s">
         <v>94</v>
-      </c>
-      <c r="AH66">
-        <v>-100</v>
-      </c>
-      <c r="AI66">
-        <v>-100</v>
-      </c>
-      <c r="AJ66">
-        <v>-100</v>
-      </c>
-      <c r="AK66">
-        <v>-100</v>
-      </c>
-      <c r="AL66">
-        <v>-100</v>
-      </c>
-      <c r="AM66">
-        <v>-100</v>
-      </c>
-      <c r="AN66">
-        <v>-100</v>
-      </c>
-      <c r="AO66">
-        <v>-100</v>
       </c>
       <c r="AP66">
         <v>-14.7</v>
@@ -48672,13 +48567,13 @@
         <v>648</v>
       </c>
       <c r="F66" t="s">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="G66" t="s">
         <v>595</v>
       </c>
       <c r="H66">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="I66" t="s">
         <v>691</v>
@@ -49455,13 +49350,13 @@
         <v>667</v>
       </c>
       <c r="F93" t="s">
-        <v>542</v>
+        <v>550</v>
       </c>
       <c r="G93" t="s">
         <v>595</v>
       </c>
       <c r="H93">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="I93" t="s">
         <v>691</v>
@@ -49484,13 +49379,13 @@
         <v>668</v>
       </c>
       <c r="F94" t="s">
-        <v>542</v>
+        <v>550</v>
       </c>
       <c r="G94" t="s">
         <v>595</v>
       </c>
       <c r="H94">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="I94" t="s">
         <v>691</v>
@@ -49513,13 +49408,13 @@
         <v>669</v>
       </c>
       <c r="F95" t="s">
-        <v>542</v>
+        <v>550</v>
       </c>
       <c r="G95" t="s">
         <v>595</v>
       </c>
       <c r="H95">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="I95" t="s">
         <v>691</v>

--- a/data/history/long/history_long.xlsx
+++ b/data/history/long/history_long.xlsx
@@ -8187,12 +8187,6 @@
       <c r="H111">
         <v>22.9268</v>
       </c>
-      <c r="I111">
-        <v>22.9268</v>
-      </c>
-      <c r="J111">
-        <v>0</v>
-      </c>
       <c r="K111">
         <v>11.3</v>
       </c>
@@ -8228,12 +8222,6 @@
       <c r="H112">
         <v>0</v>
       </c>
-      <c r="I112">
-        <v>0</v>
-      </c>
-      <c r="J112">
-        <v>0</v>
-      </c>
       <c r="K112">
         <v>62.80000000000001</v>
       </c>
@@ -8269,12 +8257,6 @@
       <c r="H113">
         <v>15.09967044335447</v>
       </c>
-      <c r="I113">
-        <v>15.09967044335447</v>
-      </c>
-      <c r="J113">
-        <v>-0.223565590534065</v>
-      </c>
       <c r="K113">
         <v>46.87817633473585</v>
       </c>
@@ -8310,12 +8292,6 @@
       <c r="H114">
         <v>3.555927309945545</v>
       </c>
-      <c r="I114">
-        <v>3.555927309945545</v>
-      </c>
-      <c r="J114">
-        <v>0.9033061050990625</v>
-      </c>
       <c r="K114">
         <v>27.21676429317348</v>
       </c>
@@ -8353,12 +8329,6 @@
       </c>
       <c r="H115">
         <v>30.87659038941771</v>
-      </c>
-      <c r="I115">
-        <v>30.87659038941771</v>
-      </c>
-      <c r="J115">
-        <v>-3.64978448421158</v>
       </c>
       <c r="K115">
         <v>60.66156020913212</v>
@@ -14373,7 +14343,7 @@
         <v>2022</v>
       </c>
       <c r="H110">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="111" spans="1:8">
@@ -14399,7 +14369,7 @@
         <v>2022</v>
       </c>
       <c r="H111">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="112" spans="1:8">
@@ -14425,7 +14395,7 @@
         <v>2022</v>
       </c>
       <c r="H112">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="113" spans="1:8">
@@ -14451,7 +14421,7 @@
         <v>2025</v>
       </c>
       <c r="H113">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="114" spans="1:8">
@@ -14477,7 +14447,7 @@
         <v>2022</v>
       </c>
       <c r="H114">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="115" spans="1:8">
@@ -37616,27 +37586,6 @@
       <c r="AC82">
         <v>22.9268</v>
       </c>
-      <c r="AD82">
-        <v>22.9268</v>
-      </c>
-      <c r="AE82">
-        <v>22.9268</v>
-      </c>
-      <c r="AF82">
-        <v>22.9268</v>
-      </c>
-      <c r="AG82">
-        <v>22.9268</v>
-      </c>
-      <c r="AH82">
-        <v>15.10000000000001</v>
-      </c>
-      <c r="AI82">
-        <v>0</v>
-      </c>
-      <c r="AJ82">
-        <v>0</v>
-      </c>
       <c r="AK82">
         <v>0</v>
       </c>
@@ -37786,27 +37735,6 @@
       <c r="AC83">
         <v>0</v>
       </c>
-      <c r="AD83">
-        <v>0</v>
-      </c>
-      <c r="AE83">
-        <v>0</v>
-      </c>
-      <c r="AF83">
-        <v>0</v>
-      </c>
-      <c r="AG83">
-        <v>0</v>
-      </c>
-      <c r="AH83">
-        <v>0</v>
-      </c>
-      <c r="AI83">
-        <v>0</v>
-      </c>
-      <c r="AJ83">
-        <v>0</v>
-      </c>
       <c r="AK83">
         <v>0</v>
       </c>
@@ -37956,27 +37884,6 @@
       <c r="AC84">
         <v>15.09967044335447</v>
       </c>
-      <c r="AD84">
-        <v>15.09967044335451</v>
-      </c>
-      <c r="AE84">
-        <v>15.09967044335447</v>
-      </c>
-      <c r="AF84">
-        <v>15.09967044335447</v>
-      </c>
-      <c r="AG84">
-        <v>15.09967044335447</v>
-      </c>
-      <c r="AH84">
-        <v>0.2789504710609521</v>
-      </c>
-      <c r="AI84">
-        <v>1.187615256060326</v>
-      </c>
-      <c r="AJ84">
-        <v>1.187615256060326</v>
-      </c>
       <c r="AK84">
         <v>-0.223565590534065</v>
       </c>
@@ -38126,27 +38033,6 @@
       <c r="AC85">
         <v>3.555927309945545</v>
       </c>
-      <c r="AD85">
-        <v>3.555927309945488</v>
-      </c>
-      <c r="AE85">
-        <v>3.555927309945488</v>
-      </c>
-      <c r="AF85">
-        <v>3.555927309945488</v>
-      </c>
-      <c r="AG85">
-        <v>3.555927309945545</v>
-      </c>
-      <c r="AH85">
-        <v>3.143148635187671</v>
-      </c>
-      <c r="AI85">
-        <v>2.221318015973026</v>
-      </c>
-      <c r="AJ85">
-        <v>1.611245316801345</v>
-      </c>
       <c r="AK85">
         <v>0.9033061050990625</v>
       </c>
@@ -38307,27 +38193,6 @@
       </c>
       <c r="AC86">
         <v>30.87659038941771</v>
-      </c>
-      <c r="AD86">
-        <v>30.87659038941769</v>
-      </c>
-      <c r="AE86">
-        <v>30.87659038941771</v>
-      </c>
-      <c r="AF86">
-        <v>30.87659038941771</v>
-      </c>
-      <c r="AG86">
-        <v>30.87659038941771</v>
-      </c>
-      <c r="AH86">
-        <v>8.375096230444328</v>
-      </c>
-      <c r="AI86">
-        <v>-1.596550984285486</v>
-      </c>
-      <c r="AJ86">
-        <v>-1.596354766042197</v>
       </c>
       <c r="AK86">
         <v>-3.64978448421158</v>
@@ -49878,7 +49743,7 @@
         <v>596</v>
       </c>
       <c r="H111">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="I111" t="s">
         <v>691</v>
@@ -49907,7 +49772,7 @@
         <v>596</v>
       </c>
       <c r="H112">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="I112" t="s">
         <v>691</v>
@@ -49936,7 +49801,7 @@
         <v>596</v>
       </c>
       <c r="H113">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="I113" t="s">
         <v>691</v>
@@ -49965,7 +49830,7 @@
         <v>596</v>
       </c>
       <c r="H114">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="I114" t="s">
         <v>691</v>
@@ -49994,7 +49859,7 @@
         <v>596</v>
       </c>
       <c r="H115">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="I115" t="s">
         <v>691</v>

--- a/data/history/long/history_long.xlsx
+++ b/data/history/long/history_long.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2904" uniqueCount="743">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2904" uniqueCount="744">
   <si>
     <t>code</t>
   </si>
@@ -1280,7 +1280,7 @@
     <t>НБУ API (Госстат); НБУ Wages_m.xlsx; пропуски из MacroStat; до 2010 — НБУ Wages_y.xlsx (Госстат)</t>
   </si>
   <si>
-    <t>НБУ API (платёжный баланс); до 2010 — Всемирный банк (платёжный баланс)</t>
+    <t>НБУ API и BOP_m.xlsx (платёжный баланс); до 2010 — Всемирный банк (платёжный баланс)</t>
   </si>
   <si>
     <t>расчёт; до 2010 — Всемирный банк (платёжный баланс)</t>
@@ -1412,10 +1412,10 @@
     <t>Из кварталов (AVG): Средняя месячная зарплата, среднее за квартал; 2010–2012 из файла НБУ Wages_m; оставшиеся пропуски 2022–2024 из квартальных данных Госстата (лист Salary). До 2010: Среднемесячная зарплата за год</t>
   </si>
   <si>
-    <t>Из кварталов (SUM): Товары и услуги, кредит, сумма месяцев. До 2010: BX.GSR.GNFS.CD / 1e6</t>
-  </si>
-  <si>
-    <t>Из кварталов (SUM): Товары и услуги, дебет, сумма месяцев. До 2010: BM.GSR.GNFS.CD / 1e6</t>
+    <t>Из кварталов (SUM): Товары и услуги, кредит, сумма месяцев; последние месяцы до API из файла BOP_m. До 2010: BX.GSR.GNFS.CD / 1e6</t>
+  </si>
+  <si>
+    <t>Из кварталов (SUM): Товары и услуги, дебет, сумма месяцев; последние месяцы до API из файла BOP_m. До 2010: BM.GSR.GNFS.CD / 1e6</t>
   </si>
   <si>
     <t>Из кварталов (SUM): EXP_USD − IMP_USD. До 2010: BN.GSR.GNFS.CD / 1e6</t>
@@ -1964,6 +1964,9 @@
     <t>НБУ API (Госстат); НБУ Wages_m.xlsx; пропуски из MacroStat</t>
   </si>
   <si>
+    <t>НБУ API и BOP_m.xlsx (платёжный баланс)</t>
+  </si>
+  <si>
     <t>Номинальный ВВП 2021 г., сцепленный через реальный рост г/г (PC_C_3); внутригодовую динамику сравнивать только г/г</t>
   </si>
   <si>
@@ -2012,10 +2015,10 @@
     <t>Средняя месячная зарплата, среднее за квартал; 2010–2012 из файла НБУ Wages_m; оставшиеся пропуски 2022–2024 из квартальных данных Госстата (лист Salary)</t>
   </si>
   <si>
-    <t>Товары и услуги, кредит, сумма месяцев</t>
-  </si>
-  <si>
-    <t>Товары и услуги, дебет, сумма месяцев</t>
+    <t>Товары и услуги, кредит, сумма месяцев; последние месяцы до API из файла BOP_m</t>
+  </si>
+  <si>
+    <t>Товары и услуги, дебет, сумма месяцев; последние месяцы до API из файла BOP_m</t>
   </si>
   <si>
     <t>EXP_USD − IMP_USD</t>
@@ -18984,6 +18987,9 @@
       <c r="CI8">
         <v>39.1</v>
       </c>
+      <c r="CJ8">
+        <v>38.4</v>
+      </c>
     </row>
     <row r="9" spans="1:89">
       <c r="A9" t="s">
@@ -19251,7 +19257,7 @@
         <v>44.69044673913044</v>
       </c>
       <c r="CK9">
-        <v>44.9262125</v>
+        <v>45.02476</v>
       </c>
     </row>
     <row r="10" spans="1:89">
@@ -19520,7 +19526,7 @@
         <v>44.8624</v>
       </c>
       <c r="CK10">
-        <v>45.051</v>
+        <v>45.5293</v>
       </c>
     </row>
     <row r="11" spans="1:89">
@@ -19789,7 +19795,7 @@
         <v>16</v>
       </c>
       <c r="CK11">
-        <v>16</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="12" spans="1:89">
@@ -19994,6 +20000,9 @@
       <c r="CI12">
         <v>19.83115822623704</v>
       </c>
+      <c r="CJ12">
+        <v>19.98829703300498</v>
+      </c>
     </row>
     <row r="13" spans="1:89">
       <c r="A13" t="s">
@@ -20197,6 +20206,9 @@
       <c r="CI13">
         <v>10.05497450613516</v>
       </c>
+      <c r="CJ13">
+        <v>10.42740907713206</v>
+      </c>
     </row>
     <row r="14" spans="1:89">
       <c r="A14" t="s">
@@ -21075,6 +21087,9 @@
       <c r="CI17">
         <v>31419.66666666667</v>
       </c>
+      <c r="CJ17">
+        <v>32429.33333333333</v>
+      </c>
     </row>
     <row r="18" spans="1:88">
       <c r="A18" t="s">
@@ -21278,6 +21293,9 @@
       <c r="CI18">
         <v>14387</v>
       </c>
+      <c r="CJ18">
+        <v>12187</v>
+      </c>
     </row>
     <row r="19" spans="1:88">
       <c r="A19" t="s">
@@ -21481,6 +21499,9 @@
       <c r="CI19">
         <v>31814</v>
       </c>
+      <c r="CJ19">
+        <v>32342</v>
+      </c>
     </row>
     <row r="20" spans="1:88">
       <c r="A20" t="s">
@@ -21683,6 +21704,9 @@
       </c>
       <c r="CI20">
         <v>-17427</v>
+      </c>
+      <c r="CJ20">
+        <v>-20155</v>
       </c>
     </row>
     <row r="21" spans="1:88">
@@ -30537,6 +30561,9 @@
       <c r="CI36">
         <v>9.133333333333335</v>
       </c>
+      <c r="CJ36">
+        <v>6.199999999999998</v>
+      </c>
     </row>
     <row r="37" spans="1:88">
       <c r="A37" t="s">
@@ -30991,6 +31018,9 @@
       <c r="CI38">
         <v>914723.0858999999</v>
       </c>
+      <c r="CJ38">
+        <v>917327.197</v>
+      </c>
     </row>
     <row r="39" spans="1:88">
       <c r="A39" t="s">
@@ -31254,6 +31284,9 @@
       <c r="CI39">
         <v>4139259.1604</v>
       </c>
+      <c r="CJ39">
+        <v>4195653.3797</v>
+      </c>
     </row>
     <row r="40" spans="1:88">
       <c r="A40" t="s">
@@ -31457,6 +31490,9 @@
       <c r="CI40">
         <v>15.55165556739514</v>
       </c>
+      <c r="CJ40">
+        <v>17.75376782523249</v>
+      </c>
     </row>
     <row r="41" spans="1:88">
       <c r="A41" t="s">
@@ -31660,6 +31696,9 @@
       <c r="CI41">
         <v>29.2948390853322</v>
       </c>
+      <c r="CJ41">
+        <v>29.08101818194272</v>
+      </c>
     </row>
     <row r="42" spans="1:88">
       <c r="A42" t="s">
@@ -31863,6 +31902,9 @@
       <c r="CI42">
         <v>10.38844073943397</v>
       </c>
+      <c r="CJ42">
+        <v>10.31664473658278</v>
+      </c>
     </row>
     <row r="43" spans="1:88">
       <c r="A43" t="s">
@@ -33898,6 +33940,9 @@
       <c r="CI53">
         <v>9490799.6</v>
       </c>
+      <c r="CJ53">
+        <v>9538348.800000001</v>
+      </c>
     </row>
     <row r="54" spans="1:88">
       <c r="A54" t="s">
@@ -34976,6 +35021,9 @@
       <c r="CI61">
         <v>5466.566666666667</v>
       </c>
+      <c r="CJ61">
+        <v>5493.233333333334</v>
+      </c>
     </row>
     <row r="62" spans="1:88">
       <c r="A62" t="s">
@@ -37356,6 +37404,9 @@
       <c r="CI75">
         <v>14.7</v>
       </c>
+      <c r="CJ75">
+        <v>13.6</v>
+      </c>
     </row>
     <row r="76" spans="1:88">
       <c r="A76" t="s">
@@ -37595,6 +37646,9 @@
       <c r="CI76">
         <v>9.9</v>
       </c>
+      <c r="CJ76">
+        <v>3.4</v>
+      </c>
     </row>
     <row r="77" spans="1:88">
       <c r="A77" t="s">
@@ -39768,6 +39822,9 @@
       <c r="CI87">
         <v>6237.14266107</v>
       </c>
+      <c r="CJ87">
+        <v>4467.46851447</v>
+      </c>
     </row>
     <row r="88" spans="1:88">
       <c r="A88" t="s">
@@ -39971,6 +40028,9 @@
       <c r="CI88">
         <v>2178.587996930001</v>
       </c>
+      <c r="CJ88">
+        <v>1933.66236314</v>
+      </c>
     </row>
     <row r="89" spans="1:88">
       <c r="A89" t="s">
@@ -40174,6 +40234,9 @@
       <c r="CI89">
         <v>682.17082755</v>
       </c>
+      <c r="CJ89">
+        <v>649.24482759</v>
+      </c>
     </row>
     <row r="90" spans="1:88">
       <c r="A90" t="s">
@@ -40377,6 +40440,9 @@
       <c r="CI90">
         <v>3323.99618793</v>
       </c>
+      <c r="CJ90">
+        <v>3387.55877592</v>
+      </c>
     </row>
     <row r="91" spans="1:88">
       <c r="A91" t="s">
@@ -40580,6 +40646,9 @@
       <c r="CI91">
         <v>437.7822446900002</v>
       </c>
+      <c r="CJ91">
+        <v>411.3390702800002</v>
+      </c>
     </row>
     <row r="92" spans="1:88">
       <c r="A92" t="s">
@@ -40783,6 +40852,9 @@
       <c r="CI92">
         <v>3451.173779139996</v>
       </c>
+      <c r="CJ92">
+        <v>3109.25742917</v>
+      </c>
     </row>
     <row r="93" spans="1:88">
       <c r="A93" t="s">
@@ -40986,6 +41058,9 @@
       <c r="CI93">
         <v>533.57196893</v>
       </c>
+      <c r="CJ93">
+        <v>509.52608051</v>
+      </c>
     </row>
     <row r="94" spans="1:88">
       <c r="A94" t="s">
@@ -41189,6 +41264,9 @@
       <c r="CI94">
         <v>339.2838354299998</v>
       </c>
+      <c r="CJ94">
+        <v>311.4197745599998</v>
+      </c>
     </row>
     <row r="95" spans="1:88">
       <c r="A95" t="s">
@@ -41392,6 +41470,9 @@
       <c r="CI95">
         <v>196.9822311900001</v>
       </c>
+      <c r="CJ95">
+        <v>188.10629171</v>
+      </c>
     </row>
     <row r="96" spans="1:88">
       <c r="A96" t="s">
@@ -41595,8 +41676,11 @@
       <c r="CI96">
         <v>966.9308393500008</v>
       </c>
-    </row>
-    <row r="97" spans="1:87">
+      <c r="CJ96">
+        <v>1203.50340813</v>
+      </c>
+    </row>
+    <row r="97" spans="1:88">
       <c r="A97" t="s">
         <v>125</v>
       </c>
@@ -41798,8 +41882,11 @@
       <c r="CI97">
         <v>1227.76045312</v>
       </c>
-    </row>
-    <row r="98" spans="1:87">
+      <c r="CJ97">
+        <v>714.61069847</v>
+      </c>
+    </row>
+    <row r="98" spans="1:88">
       <c r="A98" t="s">
         <v>126</v>
       </c>
@@ -42001,8 +42088,11 @@
       <c r="CI98">
         <v>1256.43277541</v>
       </c>
-    </row>
-    <row r="99" spans="1:87">
+      <c r="CJ98">
+        <v>1208.091834829999</v>
+      </c>
+    </row>
+    <row r="99" spans="1:88">
       <c r="A99" t="s">
         <v>127</v>
       </c>
@@ -42204,8 +42294,11 @@
       <c r="CI99">
         <v>440.674090939998</v>
       </c>
-    </row>
-    <row r="100" spans="1:87">
+      <c r="CJ99">
+        <v>413.133863630001</v>
+      </c>
+    </row>
+    <row r="100" spans="1:88">
       <c r="A100" t="s">
         <v>128</v>
       </c>
@@ -42407,8 +42500,11 @@
       <c r="CI100">
         <v>11435.77814950999</v>
       </c>
-    </row>
-    <row r="101" spans="1:87">
+      <c r="CJ100">
+        <v>12807.93434983</v>
+      </c>
+    </row>
+    <row r="101" spans="1:88">
       <c r="A101" t="s">
         <v>129</v>
       </c>
@@ -42610,8 +42706,11 @@
       <c r="CI101">
         <v>435.9155225100026</v>
       </c>
-    </row>
-    <row r="102" spans="1:87">
+      <c r="CJ101">
+        <v>602.5706533399989</v>
+      </c>
+    </row>
+    <row r="102" spans="1:88">
       <c r="A102" t="s">
         <v>130</v>
       </c>
@@ -42813,8 +42912,11 @@
       <c r="CI102">
         <v>2701.816436300007</v>
       </c>
-    </row>
-    <row r="103" spans="1:87">
+      <c r="CJ102">
+        <v>1759.572064420003</v>
+      </c>
+    </row>
+    <row r="103" spans="1:88">
       <c r="A103" t="s">
         <v>131</v>
       </c>
@@ -42999,7 +43101,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="104" spans="1:87">
+    <row r="104" spans="1:88">
       <c r="A104" t="s">
         <v>132</v>
       </c>
@@ -43181,7 +43283,7 @@
         <v>243.6666666666667</v>
       </c>
     </row>
-    <row r="105" spans="1:87">
+    <row r="105" spans="1:88">
       <c r="A105" t="s">
         <v>133</v>
       </c>
@@ -43378,7 +43480,7 @@
         <v>1323.333333333333</v>
       </c>
     </row>
-    <row r="106" spans="1:87">
+    <row r="106" spans="1:88">
       <c r="A106" t="s">
         <v>134</v>
       </c>
@@ -43569,7 +43671,7 @@
         <v>463.3333333333333</v>
       </c>
     </row>
-    <row r="107" spans="1:87">
+    <row r="107" spans="1:88">
       <c r="A107" t="s">
         <v>135</v>
       </c>
@@ -43760,7 +43862,7 @@
         <v>1653117.9</v>
       </c>
     </row>
-    <row r="108" spans="1:87">
+    <row r="108" spans="1:88">
       <c r="A108" t="s">
         <v>136</v>
       </c>
@@ -43951,7 +44053,7 @@
         <v>237170.3</v>
       </c>
     </row>
-    <row r="109" spans="1:87">
+    <row r="109" spans="1:88">
       <c r="A109" t="s">
         <v>137</v>
       </c>
@@ -44142,7 +44244,7 @@
         <v>88222.2</v>
       </c>
     </row>
-    <row r="110" spans="1:87">
+    <row r="110" spans="1:88">
       <c r="A110" t="s">
         <v>138</v>
       </c>
@@ -44333,7 +44435,7 @@
         <v>78150.99999999999</v>
       </c>
     </row>
-    <row r="111" spans="1:87">
+    <row r="111" spans="1:88">
       <c r="A111" t="s">
         <v>139</v>
       </c>
@@ -44524,7 +44626,7 @@
         <v>170583</v>
       </c>
     </row>
-    <row r="112" spans="1:87">
+    <row r="112" spans="1:88">
       <c r="A112" t="s">
         <v>140</v>
       </c>
@@ -49972,7 +50074,7 @@
         <v>409</v>
       </c>
       <c r="E2" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="F2" t="s">
         <v>582</v>
@@ -49984,7 +50086,7 @@
         <v>62</v>
       </c>
       <c r="I2" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -50001,7 +50103,7 @@
         <v>409</v>
       </c>
       <c r="E3" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="F3" t="s">
         <v>582</v>
@@ -50013,7 +50115,7 @@
         <v>62</v>
       </c>
       <c r="I3" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -50030,7 +50132,7 @@
         <v>409</v>
       </c>
       <c r="E4" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="F4" t="s">
         <v>582</v>
@@ -50042,7 +50144,7 @@
         <v>62</v>
       </c>
       <c r="I4" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -50059,7 +50161,7 @@
         <v>409</v>
       </c>
       <c r="E5" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="F5" t="s">
         <v>578</v>
@@ -50071,7 +50173,7 @@
         <v>66</v>
       </c>
       <c r="I5" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -50088,7 +50190,7 @@
         <v>411</v>
       </c>
       <c r="E6" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="F6" t="s">
         <v>582</v>
@@ -50100,7 +50202,7 @@
         <v>62</v>
       </c>
       <c r="I6" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -50117,7 +50219,7 @@
         <v>409</v>
       </c>
       <c r="E7" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="F7" t="s">
         <v>566</v>
@@ -50129,7 +50231,7 @@
         <v>79</v>
       </c>
       <c r="I7" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -50146,19 +50248,19 @@
         <v>413</v>
       </c>
       <c r="E8" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="F8" t="s">
         <v>566</v>
       </c>
       <c r="G8" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="H8">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I8" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -50175,7 +50277,7 @@
         <v>414</v>
       </c>
       <c r="E9" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="F9" t="s">
         <v>558</v>
@@ -50187,7 +50289,7 @@
         <v>88</v>
       </c>
       <c r="I9" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -50204,7 +50306,7 @@
         <v>414</v>
       </c>
       <c r="E10" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="F10" t="s">
         <v>558</v>
@@ -50216,7 +50318,7 @@
         <v>88</v>
       </c>
       <c r="I10" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -50233,7 +50335,7 @@
         <v>415</v>
       </c>
       <c r="E11" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="F11" t="s">
         <v>558</v>
@@ -50245,7 +50347,7 @@
         <v>88</v>
       </c>
       <c r="I11" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -50262,19 +50364,19 @@
         <v>415</v>
       </c>
       <c r="E12" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="F12" t="s">
         <v>578</v>
       </c>
       <c r="G12" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="H12">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I12" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -50291,19 +50393,19 @@
         <v>415</v>
       </c>
       <c r="E13" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="F13" t="s">
         <v>578</v>
       </c>
       <c r="G13" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="H13">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I13" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -50320,7 +50422,7 @@
         <v>417</v>
       </c>
       <c r="E14" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="F14" t="s">
         <v>558</v>
@@ -50332,7 +50434,7 @@
         <v>84</v>
       </c>
       <c r="I14" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -50349,7 +50451,7 @@
         <v>418</v>
       </c>
       <c r="E15" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="F15" t="s">
         <v>558</v>
@@ -50361,7 +50463,7 @@
         <v>68</v>
       </c>
       <c r="I15" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -50378,7 +50480,7 @@
         <v>418</v>
       </c>
       <c r="E16" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="F16" t="s">
         <v>558</v>
@@ -50390,7 +50492,7 @@
         <v>68</v>
       </c>
       <c r="I16" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
     </row>
     <row r="17" spans="1:9">
@@ -50407,19 +50509,19 @@
         <v>647</v>
       </c>
       <c r="E17" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="F17" t="s">
         <v>578</v>
       </c>
       <c r="G17" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="H17">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I17" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
     </row>
     <row r="18" spans="1:9">
@@ -50433,22 +50535,22 @@
         <v>399</v>
       </c>
       <c r="D18" t="s">
-        <v>424</v>
+        <v>648</v>
       </c>
       <c r="E18" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="F18" t="s">
         <v>578</v>
       </c>
       <c r="G18" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="H18">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I18" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
     </row>
     <row r="19" spans="1:9">
@@ -50462,22 +50564,22 @@
         <v>399</v>
       </c>
       <c r="D19" t="s">
-        <v>424</v>
+        <v>648</v>
       </c>
       <c r="E19" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="F19" t="s">
         <v>578</v>
       </c>
       <c r="G19" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="H19">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I19" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
     </row>
     <row r="20" spans="1:9">
@@ -50494,19 +50596,19 @@
         <v>411</v>
       </c>
       <c r="E20" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="F20" t="s">
         <v>578</v>
       </c>
       <c r="G20" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="H20">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I20" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
     </row>
     <row r="21" spans="1:9">
@@ -50523,7 +50625,7 @@
         <v>415</v>
       </c>
       <c r="E21" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="F21" t="s">
         <v>558</v>
@@ -50535,7 +50637,7 @@
         <v>87</v>
       </c>
       <c r="I21" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
     </row>
     <row r="22" spans="1:9">
@@ -50552,7 +50654,7 @@
         <v>409</v>
       </c>
       <c r="E22" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="F22" t="s">
         <v>578</v>
@@ -50564,7 +50666,7 @@
         <v>66</v>
       </c>
       <c r="I22" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
     </row>
     <row r="23" spans="1:9">
@@ -50581,7 +50683,7 @@
         <v>417</v>
       </c>
       <c r="E23" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="F23" t="s">
         <v>558</v>
@@ -50593,7 +50695,7 @@
         <v>68</v>
       </c>
       <c r="I23" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
     </row>
     <row r="24" spans="1:9">
@@ -50610,7 +50712,7 @@
         <v>423</v>
       </c>
       <c r="E24" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="F24" t="s">
         <v>582</v>
@@ -50622,7 +50724,7 @@
         <v>62</v>
       </c>
       <c r="I24" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -50639,13 +50741,13 @@
         <v>411</v>
       </c>
       <c r="E25" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="H25">
         <v>0</v>
       </c>
       <c r="I25" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
     </row>
     <row r="26" spans="1:9">
@@ -50662,7 +50764,7 @@
         <v>424</v>
       </c>
       <c r="E26" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="F26" t="s">
         <v>578</v>
@@ -50674,7 +50776,7 @@
         <v>66</v>
       </c>
       <c r="I26" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
     </row>
     <row r="27" spans="1:9">
@@ -50691,13 +50793,13 @@
         <v>411</v>
       </c>
       <c r="E27" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="H27">
         <v>0</v>
       </c>
       <c r="I27" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
     </row>
     <row r="28" spans="1:9">
@@ -50714,7 +50816,7 @@
         <v>425</v>
       </c>
       <c r="E28" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F28" t="s">
         <v>581</v>
@@ -50726,7 +50828,7 @@
         <v>60</v>
       </c>
       <c r="I28" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
     </row>
     <row r="29" spans="1:9">
@@ -50743,7 +50845,7 @@
         <v>417</v>
       </c>
       <c r="E29" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="F29" t="s">
         <v>558</v>
@@ -50755,7 +50857,7 @@
         <v>80</v>
       </c>
       <c r="I29" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
     </row>
     <row r="30" spans="1:9">
@@ -50772,7 +50874,7 @@
         <v>426</v>
       </c>
       <c r="E30" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="F30" t="s">
         <v>610</v>
@@ -50784,7 +50886,7 @@
         <v>34</v>
       </c>
       <c r="I30" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
     </row>
     <row r="31" spans="1:9">
@@ -50801,7 +50903,7 @@
         <v>409</v>
       </c>
       <c r="E31" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="F31" t="s">
         <v>578</v>
@@ -50813,7 +50915,7 @@
         <v>66</v>
       </c>
       <c r="I31" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="32" spans="1:9">
@@ -50830,7 +50932,7 @@
         <v>409</v>
       </c>
       <c r="E32" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="F32" t="s">
         <v>582</v>
@@ -50842,7 +50944,7 @@
         <v>62</v>
       </c>
       <c r="I32" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="33" spans="1:9">
@@ -50859,7 +50961,7 @@
         <v>409</v>
       </c>
       <c r="E33" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="F33" t="s">
         <v>578</v>
@@ -50871,7 +50973,7 @@
         <v>66</v>
       </c>
       <c r="I33" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="34" spans="1:9">
@@ -50888,7 +50990,7 @@
         <v>409</v>
       </c>
       <c r="E34" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="F34" t="s">
         <v>582</v>
@@ -50900,7 +51002,7 @@
         <v>62</v>
       </c>
       <c r="I34" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="35" spans="1:9">
@@ -50917,7 +51019,7 @@
         <v>409</v>
       </c>
       <c r="E35" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="F35" t="s">
         <v>578</v>
@@ -50929,7 +51031,7 @@
         <v>66</v>
       </c>
       <c r="I35" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="36" spans="1:9">
@@ -50946,7 +51048,7 @@
         <v>409</v>
       </c>
       <c r="E36" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="F36" t="s">
         <v>582</v>
@@ -50958,7 +51060,7 @@
         <v>62</v>
       </c>
       <c r="I36" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="37" spans="1:9">
@@ -50975,7 +51077,7 @@
         <v>409</v>
       </c>
       <c r="E37" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="F37" t="s">
         <v>578</v>
@@ -50987,7 +51089,7 @@
         <v>66</v>
       </c>
       <c r="I37" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="38" spans="1:9">
@@ -51004,7 +51106,7 @@
         <v>409</v>
       </c>
       <c r="E38" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="F38" t="s">
         <v>582</v>
@@ -51016,7 +51118,7 @@
         <v>62</v>
       </c>
       <c r="I38" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="39" spans="1:9">
@@ -51033,7 +51135,7 @@
         <v>409</v>
       </c>
       <c r="E39" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="F39" t="s">
         <v>578</v>
@@ -51045,7 +51147,7 @@
         <v>66</v>
       </c>
       <c r="I39" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="40" spans="1:9">
@@ -51062,7 +51164,7 @@
         <v>409</v>
       </c>
       <c r="E40" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="F40" t="s">
         <v>582</v>
@@ -51074,7 +51176,7 @@
         <v>62</v>
       </c>
       <c r="I40" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="41" spans="1:9">
@@ -51091,7 +51193,7 @@
         <v>409</v>
       </c>
       <c r="E41" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="F41" t="s">
         <v>578</v>
@@ -51103,7 +51205,7 @@
         <v>66</v>
       </c>
       <c r="I41" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="42" spans="1:9">
@@ -51120,7 +51222,7 @@
         <v>409</v>
       </c>
       <c r="E42" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="F42" t="s">
         <v>582</v>
@@ -51132,7 +51234,7 @@
         <v>62</v>
       </c>
       <c r="I42" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="43" spans="1:9">
@@ -51149,7 +51251,7 @@
         <v>409</v>
       </c>
       <c r="E43" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="F43" t="s">
         <v>578</v>
@@ -51161,7 +51263,7 @@
         <v>66</v>
       </c>
       <c r="I43" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="44" spans="1:9">
@@ -51178,7 +51280,7 @@
         <v>409</v>
       </c>
       <c r="E44" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="F44" t="s">
         <v>582</v>
@@ -51190,7 +51292,7 @@
         <v>62</v>
       </c>
       <c r="I44" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="45" spans="1:9">
@@ -51207,7 +51309,7 @@
         <v>409</v>
       </c>
       <c r="E45" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="F45" t="s">
         <v>578</v>
@@ -51219,7 +51321,7 @@
         <v>66</v>
       </c>
       <c r="I45" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="46" spans="1:9">
@@ -51236,7 +51338,7 @@
         <v>409</v>
       </c>
       <c r="E46" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="F46" t="s">
         <v>582</v>
@@ -51248,7 +51350,7 @@
         <v>62</v>
       </c>
       <c r="I46" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="47" spans="1:9">
@@ -51265,7 +51367,7 @@
         <v>409</v>
       </c>
       <c r="E47" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="F47" t="s">
         <v>578</v>
@@ -51277,7 +51379,7 @@
         <v>66</v>
       </c>
       <c r="I47" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="48" spans="1:9">
@@ -51294,7 +51396,7 @@
         <v>409</v>
       </c>
       <c r="E48" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="F48" t="s">
         <v>582</v>
@@ -51306,7 +51408,7 @@
         <v>62</v>
       </c>
       <c r="I48" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="49" spans="1:9">
@@ -51323,7 +51425,7 @@
         <v>409</v>
       </c>
       <c r="E49" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="F49" t="s">
         <v>582</v>
@@ -51335,7 +51437,7 @@
         <v>62</v>
       </c>
       <c r="I49" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="50" spans="1:9">
@@ -51352,7 +51454,7 @@
         <v>409</v>
       </c>
       <c r="E50" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="F50" t="s">
         <v>578</v>
@@ -51364,7 +51466,7 @@
         <v>66</v>
       </c>
       <c r="I50" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="51" spans="1:9">
@@ -51381,7 +51483,7 @@
         <v>409</v>
       </c>
       <c r="E51" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="F51" t="s">
         <v>582</v>
@@ -51393,7 +51495,7 @@
         <v>62</v>
       </c>
       <c r="I51" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="52" spans="1:9">
@@ -51410,7 +51512,7 @@
         <v>409</v>
       </c>
       <c r="E52" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="F52" t="s">
         <v>578</v>
@@ -51422,7 +51524,7 @@
         <v>66</v>
       </c>
       <c r="I52" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="53" spans="1:9">
@@ -51439,7 +51541,7 @@
         <v>409</v>
       </c>
       <c r="E53" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="F53" t="s">
         <v>582</v>
@@ -51451,7 +51553,7 @@
         <v>62</v>
       </c>
       <c r="I53" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="54" spans="1:9">
@@ -51468,7 +51570,7 @@
         <v>409</v>
       </c>
       <c r="E54" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="F54" t="s">
         <v>578</v>
@@ -51480,7 +51582,7 @@
         <v>66</v>
       </c>
       <c r="I54" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="55" spans="1:9">
@@ -51497,7 +51599,7 @@
         <v>409</v>
       </c>
       <c r="E55" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="F55" t="s">
         <v>582</v>
@@ -51509,7 +51611,7 @@
         <v>62</v>
       </c>
       <c r="I55" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="56" spans="1:9">
@@ -51526,7 +51628,7 @@
         <v>409</v>
       </c>
       <c r="E56" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="F56" t="s">
         <v>578</v>
@@ -51538,7 +51640,7 @@
         <v>66</v>
       </c>
       <c r="I56" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="57" spans="1:9">
@@ -51555,7 +51657,7 @@
         <v>409</v>
       </c>
       <c r="E57" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="F57" t="s">
         <v>578</v>
@@ -51567,7 +51669,7 @@
         <v>66</v>
       </c>
       <c r="I57" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="58" spans="1:9">
@@ -51584,7 +51686,7 @@
         <v>409</v>
       </c>
       <c r="E58" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="F58" t="s">
         <v>582</v>
@@ -51596,7 +51698,7 @@
         <v>62</v>
       </c>
       <c r="I58" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="59" spans="1:9">
@@ -51613,7 +51715,7 @@
         <v>409</v>
       </c>
       <c r="E59" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="F59" t="s">
         <v>578</v>
@@ -51625,7 +51727,7 @@
         <v>66</v>
       </c>
       <c r="I59" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="60" spans="1:9">
@@ -51642,7 +51744,7 @@
         <v>409</v>
       </c>
       <c r="E60" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="F60" t="s">
         <v>582</v>
@@ -51654,7 +51756,7 @@
         <v>62</v>
       </c>
       <c r="I60" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="61" spans="1:9">
@@ -51671,7 +51773,7 @@
         <v>409</v>
       </c>
       <c r="E61" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="F61" t="s">
         <v>578</v>
@@ -51683,7 +51785,7 @@
         <v>66</v>
       </c>
       <c r="I61" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="62" spans="1:9">
@@ -51700,7 +51802,7 @@
         <v>409</v>
       </c>
       <c r="E62" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="F62" t="s">
         <v>566</v>
@@ -51712,7 +51814,7 @@
         <v>79</v>
       </c>
       <c r="I62" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="63" spans="1:9">
@@ -51729,7 +51831,7 @@
         <v>427</v>
       </c>
       <c r="E63" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="F63" t="s">
         <v>582</v>
@@ -51741,7 +51843,7 @@
         <v>63</v>
       </c>
       <c r="I63" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="64" spans="1:9">
@@ -51758,7 +51860,7 @@
         <v>428</v>
       </c>
       <c r="E64" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="F64" t="s">
         <v>578</v>
@@ -51770,7 +51872,7 @@
         <v>66</v>
       </c>
       <c r="I64" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="65" spans="1:9">
@@ -51787,19 +51889,19 @@
         <v>409</v>
       </c>
       <c r="E65" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="F65" t="s">
         <v>578</v>
       </c>
       <c r="G65" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="H65">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I65" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="66" spans="1:9">
@@ -51816,7 +51918,7 @@
         <v>409</v>
       </c>
       <c r="E66" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="F66" t="s">
         <v>582</v>
@@ -51828,7 +51930,7 @@
         <v>62</v>
       </c>
       <c r="I66" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="67" spans="1:9">
@@ -51845,19 +51947,19 @@
         <v>415</v>
       </c>
       <c r="E67" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="F67" t="s">
         <v>558</v>
       </c>
       <c r="G67" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="H67">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I67" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="68" spans="1:9">
@@ -51874,19 +51976,19 @@
         <v>415</v>
       </c>
       <c r="E68" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="F68" t="s">
         <v>558</v>
       </c>
       <c r="G68" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="H68">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I68" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="69" spans="1:9">
@@ -51903,19 +52005,19 @@
         <v>415</v>
       </c>
       <c r="E69" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="F69" t="s">
         <v>578</v>
       </c>
       <c r="G69" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="H69">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I69" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="70" spans="1:9">
@@ -51932,19 +52034,19 @@
         <v>415</v>
       </c>
       <c r="E70" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="F70" t="s">
         <v>578</v>
       </c>
       <c r="G70" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="H70">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I70" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="71" spans="1:9">
@@ -51961,19 +52063,19 @@
         <v>415</v>
       </c>
       <c r="E71" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="F71" t="s">
         <v>578</v>
       </c>
       <c r="G71" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="H71">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I71" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="72" spans="1:9">
@@ -51990,7 +52092,7 @@
         <v>423</v>
       </c>
       <c r="E72" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="F72" t="s">
         <v>582</v>
@@ -52002,7 +52104,7 @@
         <v>62</v>
       </c>
       <c r="I72" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="73" spans="1:9">
@@ -52019,7 +52121,7 @@
         <v>423</v>
       </c>
       <c r="E73" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="F73" t="s">
         <v>582</v>
@@ -52031,7 +52133,7 @@
         <v>60</v>
       </c>
       <c r="I73" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="74" spans="1:9">
@@ -52048,7 +52150,7 @@
         <v>423</v>
       </c>
       <c r="E74" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="F74" t="s">
         <v>582</v>
@@ -52060,7 +52162,7 @@
         <v>62</v>
       </c>
       <c r="I74" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="75" spans="1:9">
@@ -52077,7 +52179,7 @@
         <v>424</v>
       </c>
       <c r="E75" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="F75" t="s">
         <v>578</v>
@@ -52089,7 +52191,7 @@
         <v>66</v>
       </c>
       <c r="I75" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="76" spans="1:9">
@@ -52106,7 +52208,7 @@
         <v>424</v>
       </c>
       <c r="E76" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="F76" t="s">
         <v>578</v>
@@ -52118,7 +52220,7 @@
         <v>66</v>
       </c>
       <c r="I76" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="77" spans="1:9">
@@ -52135,7 +52237,7 @@
         <v>424</v>
       </c>
       <c r="E77" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="F77" t="s">
         <v>578</v>
@@ -52147,7 +52249,7 @@
         <v>66</v>
       </c>
       <c r="I77" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="78" spans="1:9">
@@ -52164,7 +52266,7 @@
         <v>424</v>
       </c>
       <c r="E78" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="F78" t="s">
         <v>578</v>
@@ -52176,7 +52278,7 @@
         <v>66</v>
       </c>
       <c r="I78" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="79" spans="1:9">
@@ -52193,7 +52295,7 @@
         <v>415</v>
       </c>
       <c r="E79" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="F79" t="s">
         <v>586</v>
@@ -52205,7 +52307,7 @@
         <v>59</v>
       </c>
       <c r="I79" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="80" spans="1:9">
@@ -52222,7 +52324,7 @@
         <v>415</v>
       </c>
       <c r="E80" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="F80" t="s">
         <v>598</v>
@@ -52234,7 +52336,7 @@
         <v>46</v>
       </c>
       <c r="I80" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="81" spans="1:9">
@@ -52251,7 +52353,7 @@
         <v>415</v>
       </c>
       <c r="E81" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="F81" t="s">
         <v>598</v>
@@ -52263,7 +52365,7 @@
         <v>46</v>
       </c>
       <c r="I81" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="82" spans="1:9">
@@ -52280,19 +52382,19 @@
         <v>425</v>
       </c>
       <c r="E82" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="F82" t="s">
         <v>577</v>
       </c>
       <c r="G82" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="H82">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I82" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="83" spans="1:9">
@@ -52309,7 +52411,7 @@
         <v>429</v>
       </c>
       <c r="E83" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="F83" t="s">
         <v>562</v>
@@ -52321,7 +52423,7 @@
         <v>82</v>
       </c>
       <c r="I83" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="84" spans="1:9">
@@ -52338,7 +52440,7 @@
         <v>430</v>
       </c>
       <c r="E84" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="F84" t="s">
         <v>626</v>
@@ -52350,7 +52452,7 @@
         <v>16</v>
       </c>
       <c r="I84" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="85" spans="1:9">
@@ -52367,7 +52469,7 @@
         <v>431</v>
       </c>
       <c r="E85" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="F85" t="s">
         <v>626</v>
@@ -52379,7 +52481,7 @@
         <v>19</v>
       </c>
       <c r="I85" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="86" spans="1:9">
@@ -52396,7 +52498,7 @@
         <v>431</v>
       </c>
       <c r="E86" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="F86" t="s">
         <v>626</v>
@@ -52408,7 +52510,7 @@
         <v>19</v>
       </c>
       <c r="I86" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="87" spans="1:9">
@@ -52425,7 +52527,7 @@
         <v>432</v>
       </c>
       <c r="E87" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="F87" t="s">
         <v>593</v>
@@ -52437,7 +52539,7 @@
         <v>51</v>
       </c>
       <c r="I87" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="88" spans="1:9">
@@ -52454,7 +52556,7 @@
         <v>432</v>
       </c>
       <c r="E88" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="F88" t="s">
         <v>593</v>
@@ -52466,7 +52568,7 @@
         <v>51</v>
       </c>
       <c r="I88" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="89" spans="1:9">
@@ -52483,7 +52585,7 @@
         <v>432</v>
       </c>
       <c r="E89" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="F89" t="s">
         <v>593</v>
@@ -52495,7 +52597,7 @@
         <v>51</v>
       </c>
       <c r="I89" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="90" spans="1:9">
@@ -52512,19 +52614,19 @@
         <v>433</v>
       </c>
       <c r="E90" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="F90" t="s">
         <v>578</v>
       </c>
       <c r="G90" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="H90">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I90" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="91" spans="1:9">
@@ -52541,7 +52643,7 @@
         <v>434</v>
       </c>
       <c r="E91" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="F91" t="s">
         <v>558</v>
@@ -52553,7 +52655,7 @@
         <v>68</v>
       </c>
       <c r="I91" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="92" spans="1:9">
@@ -52570,7 +52672,7 @@
         <v>409</v>
       </c>
       <c r="E92" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="F92" t="s">
         <v>590</v>
@@ -52582,7 +52684,7 @@
         <v>54</v>
       </c>
       <c r="I92" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="93" spans="1:9">
@@ -52599,7 +52701,7 @@
         <v>409</v>
       </c>
       <c r="E93" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F93" t="s">
         <v>598</v>
@@ -52611,7 +52713,7 @@
         <v>46</v>
       </c>
       <c r="I93" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="94" spans="1:9">
@@ -52628,7 +52730,7 @@
         <v>409</v>
       </c>
       <c r="E94" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="F94" t="s">
         <v>598</v>
@@ -52640,7 +52742,7 @@
         <v>46</v>
       </c>
       <c r="I94" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="95" spans="1:9">
@@ -52657,7 +52759,7 @@
         <v>409</v>
       </c>
       <c r="E95" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="F95" t="s">
         <v>598</v>
@@ -52669,7 +52771,7 @@
         <v>46</v>
       </c>
       <c r="I95" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="96" spans="1:9">
@@ -52686,7 +52788,7 @@
         <v>409</v>
       </c>
       <c r="E96" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="F96" t="s">
         <v>590</v>
@@ -52698,7 +52800,7 @@
         <v>54</v>
       </c>
       <c r="I96" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="97" spans="1:9">
@@ -52715,7 +52817,7 @@
         <v>409</v>
       </c>
       <c r="E97" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="F97" t="s">
         <v>590</v>
@@ -52727,7 +52829,7 @@
         <v>54</v>
       </c>
       <c r="I97" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="98" spans="1:9">
@@ -52744,7 +52846,7 @@
         <v>409</v>
       </c>
       <c r="E98" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="F98" t="s">
         <v>590</v>
@@ -52756,7 +52858,7 @@
         <v>54</v>
       </c>
       <c r="I98" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="99" spans="1:9">
@@ -52773,7 +52875,7 @@
         <v>409</v>
       </c>
       <c r="E99" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="F99" t="s">
         <v>590</v>
@@ -52785,7 +52887,7 @@
         <v>54</v>
       </c>
       <c r="I99" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="100" spans="1:9">
@@ -52802,7 +52904,7 @@
         <v>409</v>
       </c>
       <c r="E100" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="F100" t="s">
         <v>590</v>
@@ -52814,7 +52916,7 @@
         <v>54</v>
       </c>
       <c r="I100" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="101" spans="1:9">
@@ -52831,7 +52933,7 @@
         <v>409</v>
       </c>
       <c r="E101" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="F101" t="s">
         <v>590</v>
@@ -52843,7 +52945,7 @@
         <v>54</v>
       </c>
       <c r="I101" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="102" spans="1:9">
@@ -52860,7 +52962,7 @@
         <v>409</v>
       </c>
       <c r="E102" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="F102" t="s">
         <v>590</v>
@@ -52872,7 +52974,7 @@
         <v>54</v>
       </c>
       <c r="I102" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="103" spans="1:9">
@@ -52889,7 +52991,7 @@
         <v>409</v>
       </c>
       <c r="E103" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="F103" t="s">
         <v>590</v>
@@ -52901,7 +53003,7 @@
         <v>54</v>
       </c>
       <c r="I103" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="104" spans="1:9">
@@ -52918,19 +53020,19 @@
         <v>435</v>
       </c>
       <c r="E104" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="F104" t="s">
         <v>566</v>
       </c>
       <c r="G104" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="H104">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I104" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="105" spans="1:9">
@@ -52947,19 +53049,19 @@
         <v>435</v>
       </c>
       <c r="E105" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="F105" t="s">
         <v>566</v>
       </c>
       <c r="G105" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="H105">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I105" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="106" spans="1:9">
@@ -52976,7 +53078,7 @@
         <v>409</v>
       </c>
       <c r="E106" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="F106" t="s">
         <v>566</v>
@@ -52988,7 +53090,7 @@
         <v>79</v>
       </c>
       <c r="I106" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="107" spans="1:9">
@@ -53005,7 +53107,7 @@
         <v>409</v>
       </c>
       <c r="E107" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="F107" t="s">
         <v>566</v>
@@ -53017,7 +53119,7 @@
         <v>79</v>
       </c>
       <c r="I107" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="108" spans="1:9">
@@ -53034,7 +53136,7 @@
         <v>409</v>
       </c>
       <c r="E108" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="F108" t="s">
         <v>566</v>
@@ -53046,7 +53148,7 @@
         <v>79</v>
       </c>
       <c r="I108" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="109" spans="1:9">
@@ -53063,7 +53165,7 @@
         <v>409</v>
       </c>
       <c r="E109" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="F109" t="s">
         <v>566</v>
@@ -53075,7 +53177,7 @@
         <v>79</v>
       </c>
       <c r="I109" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="110" spans="1:9">
@@ -53092,7 +53194,7 @@
         <v>409</v>
       </c>
       <c r="E110" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="F110" t="s">
         <v>566</v>
@@ -53104,7 +53206,7 @@
         <v>79</v>
       </c>
       <c r="I110" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="111" spans="1:9">
@@ -53121,7 +53223,7 @@
         <v>436</v>
       </c>
       <c r="E111" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="F111" t="s">
         <v>581</v>
@@ -53133,7 +53235,7 @@
         <v>48</v>
       </c>
       <c r="I111" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="112" spans="1:9">
@@ -53150,7 +53252,7 @@
         <v>436</v>
       </c>
       <c r="E112" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="F112" t="s">
         <v>581</v>
@@ -53162,7 +53264,7 @@
         <v>48</v>
       </c>
       <c r="I112" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="113" spans="1:9">
@@ -53179,7 +53281,7 @@
         <v>436</v>
       </c>
       <c r="E113" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="F113" t="s">
         <v>581</v>
@@ -53191,7 +53293,7 @@
         <v>48</v>
       </c>
       <c r="I113" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="114" spans="1:9">
@@ -53208,7 +53310,7 @@
         <v>436</v>
       </c>
       <c r="E114" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="F114" t="s">
         <v>581</v>
@@ -53220,7 +53322,7 @@
         <v>52</v>
       </c>
       <c r="I114" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="115" spans="1:9">
@@ -53237,7 +53339,7 @@
         <v>436</v>
       </c>
       <c r="E115" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="F115" t="s">
         <v>581</v>
@@ -53249,7 +53351,7 @@
         <v>49</v>
       </c>
       <c r="I115" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="116" spans="1:9">
@@ -53266,19 +53368,19 @@
         <v>437</v>
       </c>
       <c r="E116" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="F116" t="s">
         <v>578</v>
       </c>
       <c r="G116" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="H116">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I116" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="117" spans="1:9">
@@ -53295,19 +53397,19 @@
         <v>437</v>
       </c>
       <c r="E117" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="F117" t="s">
         <v>578</v>
       </c>
       <c r="G117" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="H117">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I117" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="118" spans="1:9">
@@ -53324,19 +53426,19 @@
         <v>437</v>
       </c>
       <c r="E118" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="F118" t="s">
         <v>578</v>
       </c>
       <c r="G118" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="H118">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I118" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="119" spans="1:9">
@@ -53353,19 +53455,19 @@
         <v>437</v>
       </c>
       <c r="E119" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="F119" t="s">
         <v>578</v>
       </c>
       <c r="G119" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="H119">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I119" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="120" spans="1:9">
@@ -53382,19 +53484,19 @@
         <v>437</v>
       </c>
       <c r="E120" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="F120" t="s">
         <v>578</v>
       </c>
       <c r="G120" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="H120">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I120" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="121" spans="1:9">
@@ -53411,19 +53513,19 @@
         <v>437</v>
       </c>
       <c r="E121" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="F121" t="s">
         <v>578</v>
       </c>
       <c r="G121" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="H121">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I121" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="122" spans="1:9">
@@ -53440,19 +53542,19 @@
         <v>437</v>
       </c>
       <c r="E122" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="F122" t="s">
         <v>578</v>
       </c>
       <c r="G122" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="H122">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I122" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="123" spans="1:9">
@@ -53469,19 +53571,19 @@
         <v>437</v>
       </c>
       <c r="E123" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="F123" t="s">
         <v>578</v>
       </c>
       <c r="G123" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="H123">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I123" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="124" spans="1:9">
@@ -53498,19 +53600,19 @@
         <v>437</v>
       </c>
       <c r="E124" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="F124" t="s">
         <v>578</v>
       </c>
       <c r="G124" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="H124">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I124" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="125" spans="1:9">
@@ -53527,19 +53629,19 @@
         <v>437</v>
       </c>
       <c r="E125" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="F125" t="s">
         <v>578</v>
       </c>
       <c r="G125" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="H125">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I125" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="126" spans="1:9">
@@ -53556,19 +53658,19 @@
         <v>437</v>
       </c>
       <c r="E126" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="F126" t="s">
         <v>578</v>
       </c>
       <c r="G126" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="H126">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I126" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="127" spans="1:9">
@@ -53585,19 +53687,19 @@
         <v>437</v>
       </c>
       <c r="E127" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="F127" t="s">
         <v>578</v>
       </c>
       <c r="G127" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="H127">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I127" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="128" spans="1:9">
@@ -53614,19 +53716,19 @@
         <v>437</v>
       </c>
       <c r="E128" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="F128" t="s">
         <v>578</v>
       </c>
       <c r="G128" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="H128">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I128" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="129" spans="1:9">
@@ -53643,19 +53745,19 @@
         <v>437</v>
       </c>
       <c r="E129" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="F129" t="s">
         <v>578</v>
       </c>
       <c r="G129" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="H129">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I129" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="130" spans="1:9">
@@ -53672,19 +53774,19 @@
         <v>437</v>
       </c>
       <c r="E130" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="F130" t="s">
         <v>578</v>
       </c>
       <c r="G130" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="H130">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I130" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="131" spans="1:9">
@@ -53701,19 +53803,19 @@
         <v>437</v>
       </c>
       <c r="E131" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="F131" t="s">
         <v>578</v>
       </c>
       <c r="G131" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="H131">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I131" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="132" spans="1:9">
@@ -53730,7 +53832,7 @@
         <v>438</v>
       </c>
       <c r="E132" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="F132" t="s">
         <v>579</v>
@@ -53742,7 +53844,7 @@
         <v>60</v>
       </c>
       <c r="I132" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="133" spans="1:9">
@@ -53759,7 +53861,7 @@
         <v>438</v>
       </c>
       <c r="E133" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="F133" t="s">
         <v>579</v>
@@ -53771,7 +53873,7 @@
         <v>59</v>
       </c>
       <c r="I133" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="134" spans="1:9">
@@ -53788,7 +53890,7 @@
         <v>438</v>
       </c>
       <c r="E134" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="F134" t="s">
         <v>579</v>
@@ -53800,7 +53902,7 @@
         <v>64</v>
       </c>
       <c r="I134" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="135" spans="1:9">
@@ -53817,7 +53919,7 @@
         <v>438</v>
       </c>
       <c r="E135" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="F135" t="s">
         <v>581</v>
@@ -53829,7 +53931,7 @@
         <v>62</v>
       </c>
       <c r="I135" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="136" spans="1:9">
@@ -53846,7 +53948,7 @@
         <v>439</v>
       </c>
       <c r="E136" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="F136" t="s">
         <v>582</v>
@@ -53858,7 +53960,7 @@
         <v>62</v>
       </c>
       <c r="I136" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="137" spans="1:9">
@@ -53875,7 +53977,7 @@
         <v>439</v>
       </c>
       <c r="E137" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="F137" t="s">
         <v>582</v>
@@ -53887,7 +53989,7 @@
         <v>62</v>
       </c>
       <c r="I137" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="138" spans="1:9">
@@ -53904,7 +54006,7 @@
         <v>439</v>
       </c>
       <c r="E138" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="F138" t="s">
         <v>582</v>
@@ -53916,7 +54018,7 @@
         <v>62</v>
       </c>
       <c r="I138" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="139" spans="1:9">
@@ -53933,7 +54035,7 @@
         <v>439</v>
       </c>
       <c r="E139" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="F139" t="s">
         <v>582</v>
@@ -53945,7 +54047,7 @@
         <v>62</v>
       </c>
       <c r="I139" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="140" spans="1:9">
@@ -53962,7 +54064,7 @@
         <v>439</v>
       </c>
       <c r="E140" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="F140" t="s">
         <v>582</v>
@@ -53974,7 +54076,7 @@
         <v>62</v>
       </c>
       <c r="I140" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="141" spans="1:9">
@@ -53991,7 +54093,7 @@
         <v>439</v>
       </c>
       <c r="E141" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="F141" t="s">
         <v>582</v>
@@ -54003,7 +54105,7 @@
         <v>62</v>
       </c>
       <c r="I141" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="142" spans="1:9">
@@ -54020,7 +54122,7 @@
         <v>439</v>
       </c>
       <c r="E142" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="F142" t="s">
         <v>582</v>
@@ -54032,7 +54134,7 @@
         <v>62</v>
       </c>
       <c r="I142" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="143" spans="1:9">
@@ -54049,7 +54151,7 @@
         <v>439</v>
       </c>
       <c r="E143" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="F143" t="s">
         <v>582</v>
@@ -54061,7 +54163,7 @@
         <v>62</v>
       </c>
       <c r="I143" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="144" spans="1:9">
@@ -54078,7 +54180,7 @@
         <v>439</v>
       </c>
       <c r="E144" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="F144" t="s">
         <v>582</v>
@@ -54090,7 +54192,7 @@
         <v>62</v>
       </c>
       <c r="I144" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="145" spans="1:9">
@@ -54107,7 +54209,7 @@
         <v>439</v>
       </c>
       <c r="E145" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="F145" t="s">
         <v>582</v>
@@ -54119,7 +54221,7 @@
         <v>62</v>
       </c>
       <c r="I145" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="146" spans="1:9">
@@ -54136,7 +54238,7 @@
         <v>439</v>
       </c>
       <c r="E146" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="F146" t="s">
         <v>582</v>
@@ -54148,7 +54250,7 @@
         <v>62</v>
       </c>
       <c r="I146" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="147" spans="1:9">
@@ -54165,7 +54267,7 @@
         <v>439</v>
       </c>
       <c r="E147" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="F147" t="s">
         <v>582</v>
@@ -54177,7 +54279,7 @@
         <v>62</v>
       </c>
       <c r="I147" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="148" spans="1:9">
@@ -54194,7 +54296,7 @@
         <v>439</v>
       </c>
       <c r="E148" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="F148" t="s">
         <v>582</v>
@@ -54206,7 +54308,7 @@
         <v>62</v>
       </c>
       <c r="I148" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="149" spans="1:9">
@@ -54223,7 +54325,7 @@
         <v>439</v>
       </c>
       <c r="E149" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="F149" t="s">
         <v>582</v>
@@ -54235,7 +54337,7 @@
         <v>62</v>
       </c>
       <c r="I149" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="150" spans="1:9">
@@ -54252,7 +54354,7 @@
         <v>439</v>
       </c>
       <c r="E150" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="F150" t="s">
         <v>582</v>
@@ -54264,7 +54366,7 @@
         <v>62</v>
       </c>
       <c r="I150" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="151" spans="1:9">
@@ -54281,7 +54383,7 @@
         <v>439</v>
       </c>
       <c r="E151" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="F151" t="s">
         <v>582</v>
@@ -54293,7 +54395,7 @@
         <v>62</v>
       </c>
       <c r="I151" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="152" spans="1:9">
@@ -54310,7 +54412,7 @@
         <v>439</v>
       </c>
       <c r="E152" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="F152" t="s">
         <v>582</v>
@@ -54322,7 +54424,7 @@
         <v>62</v>
       </c>
       <c r="I152" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="153" spans="1:9">
@@ -54339,7 +54441,7 @@
         <v>439</v>
       </c>
       <c r="E153" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="F153" t="s">
         <v>582</v>
@@ -54351,7 +54453,7 @@
         <v>62</v>
       </c>
       <c r="I153" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="154" spans="1:9">
@@ -54368,7 +54470,7 @@
         <v>439</v>
       </c>
       <c r="E154" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="F154" t="s">
         <v>582</v>
@@ -54380,7 +54482,7 @@
         <v>62</v>
       </c>
       <c r="I154" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="155" spans="1:9">
@@ -54397,7 +54499,7 @@
         <v>439</v>
       </c>
       <c r="E155" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="F155" t="s">
         <v>582</v>
@@ -54409,7 +54511,7 @@
         <v>62</v>
       </c>
       <c r="I155" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="156" spans="1:9">
@@ -54426,7 +54528,7 @@
         <v>439</v>
       </c>
       <c r="E156" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="F156" t="s">
         <v>582</v>
@@ -54438,7 +54540,7 @@
         <v>62</v>
       </c>
       <c r="I156" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="157" spans="1:9">
@@ -54455,7 +54557,7 @@
         <v>439</v>
       </c>
       <c r="E157" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="F157" t="s">
         <v>582</v>
@@ -54467,7 +54569,7 @@
         <v>62</v>
       </c>
       <c r="I157" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="158" spans="1:9">
@@ -54484,7 +54586,7 @@
         <v>440</v>
       </c>
       <c r="E158" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="F158" t="s">
         <v>634</v>
@@ -54496,7 +54598,7 @@
         <v>11</v>
       </c>
       <c r="I158" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="159" spans="1:9">
@@ -54513,7 +54615,7 @@
         <v>440</v>
       </c>
       <c r="E159" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="F159" t="s">
         <v>634</v>
@@ -54525,7 +54627,7 @@
         <v>11</v>
       </c>
       <c r="I159" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="160" spans="1:9">
@@ -54542,7 +54644,7 @@
         <v>440</v>
       </c>
       <c r="E160" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="F160" t="s">
         <v>634</v>
@@ -54554,7 +54656,7 @@
         <v>11</v>
       </c>
       <c r="I160" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="161" spans="1:9">
@@ -54571,7 +54673,7 @@
         <v>441</v>
       </c>
       <c r="E161" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="F161" t="s">
         <v>590</v>
@@ -54583,7 +54685,7 @@
         <v>56</v>
       </c>
       <c r="I161" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="162" spans="1:9">
@@ -54600,7 +54702,7 @@
         <v>441</v>
       </c>
       <c r="E162" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="F162" t="s">
         <v>590</v>
@@ -54612,7 +54714,7 @@
         <v>55</v>
       </c>
       <c r="I162" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="163" spans="1:9">
@@ -54629,7 +54731,7 @@
         <v>441</v>
       </c>
       <c r="E163" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="F163" t="s">
         <v>596</v>
@@ -54641,7 +54743,7 @@
         <v>49</v>
       </c>
       <c r="I163" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="164" spans="1:9">
@@ -54658,7 +54760,7 @@
         <v>441</v>
       </c>
       <c r="E164" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="F164" t="s">
         <v>596</v>
@@ -54670,7 +54772,7 @@
         <v>50</v>
       </c>
       <c r="I164" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="165" spans="1:9">
@@ -54687,7 +54789,7 @@
         <v>442</v>
       </c>
       <c r="E165" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="F165" t="s">
         <v>590</v>
@@ -54699,7 +54801,7 @@
         <v>56</v>
       </c>
       <c r="I165" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="166" spans="1:9">
@@ -54716,7 +54818,7 @@
         <v>442</v>
       </c>
       <c r="E166" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="F166" t="s">
         <v>590</v>
@@ -54728,7 +54830,7 @@
         <v>55</v>
       </c>
       <c r="I166" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="167" spans="1:9">
@@ -54745,7 +54847,7 @@
         <v>442</v>
       </c>
       <c r="E167" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="F167" t="s">
         <v>596</v>
@@ -54757,7 +54859,7 @@
         <v>49</v>
       </c>
       <c r="I167" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="168" spans="1:9">
@@ -54774,7 +54876,7 @@
         <v>442</v>
       </c>
       <c r="E168" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="F168" t="s">
         <v>596</v>
@@ -54786,7 +54888,7 @@
         <v>50</v>
       </c>
       <c r="I168" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="169" spans="1:9">
@@ -54803,7 +54905,7 @@
         <v>443</v>
       </c>
       <c r="E169" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="F169" t="s">
         <v>607</v>
@@ -54815,7 +54917,7 @@
         <v>37</v>
       </c>
       <c r="I169" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="170" spans="1:9">
@@ -54832,7 +54934,7 @@
         <v>443</v>
       </c>
       <c r="E170" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="F170" t="s">
         <v>607</v>
@@ -54844,7 +54946,7 @@
         <v>37</v>
       </c>
       <c r="I170" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="171" spans="1:9">
@@ -54861,7 +54963,7 @@
         <v>443</v>
       </c>
       <c r="E171" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="F171" t="s">
         <v>614</v>
@@ -54873,7 +54975,7 @@
         <v>30</v>
       </c>
       <c r="I171" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="172" spans="1:9">
@@ -54890,7 +54992,7 @@
         <v>443</v>
       </c>
       <c r="E172" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="F172" t="s">
         <v>630</v>
@@ -54902,7 +55004,7 @@
         <v>14</v>
       </c>
       <c r="I172" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="173" spans="1:9">
@@ -54919,7 +55021,7 @@
         <v>443</v>
       </c>
       <c r="E173" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="F173" t="s">
         <v>630</v>
@@ -54931,7 +55033,7 @@
         <v>14</v>
       </c>
       <c r="I173" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="174" spans="1:9">
@@ -54948,7 +55050,7 @@
         <v>443</v>
       </c>
       <c r="E174" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="F174" t="s">
         <v>630</v>
@@ -54960,7 +55062,7 @@
         <v>14</v>
       </c>
       <c r="I174" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="175" spans="1:9">
@@ -54977,7 +55079,7 @@
         <v>444</v>
       </c>
       <c r="E175" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="F175" t="s">
         <v>558</v>
@@ -54989,7 +55091,7 @@
         <v>87</v>
       </c>
       <c r="I175" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
   </sheetData>
